--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_30-01-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_30-01-2026.xlsx
@@ -608,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>£10.15</t>
+          <t>£11.17</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>£14.53</t>
+          <t>£15.98</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>£11.87</t>
+          <t>£13.05</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>£15.15</t>
+          <t>£16.66</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>£19.41</t>
+          <t>£21.35</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>£15.71</t>
+          <t>£17.30</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>£19.22</t>
+          <t>£21.13</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>£22.14</t>
+          <t>£24.35</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>£21.34</t>
+          <t>£23.47</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>£23.98</t>
+          <t>£26.39</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>£27.08</t>
+          <t>£29.78</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>£26.67</t>
+          <t>£29.33</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>£39.35</t>
+          <t>£43.29</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>£32.74</t>
+          <t>£36.01</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>£33.13</t>
+          <t>£36.45</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>£40.04</t>
+          <t>£44.04</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>£49.78</t>
+          <t>£54.76</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>£40.45</t>
+          <t>£44.49</t>
         </is>
       </c>
     </row>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>£852.50 Pre Sale Price-£889.80</t>
+          <t>£891.67</t>
         </is>
       </c>
     </row>
@@ -2132,12 +2132,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>£34.56</t>
+          <t>£38.02</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>£36.95</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>£53.63</t>
+          <t>£58.99</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>£58.14</t>
+          <t>£63.95</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>£46.36</t>
+          <t>£51.00</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>£45.63</t>
+          <t>£50.20</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>£43.97</t>
+          <t>£48.37</t>
         </is>
       </c>
     </row>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>£1257.76</t>
+          <t>£1333.28</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>£1366.4</t>
+          <t>£1533.28</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>£1358.08</t>
+          <t>£1517.76</t>
         </is>
       </c>
     </row>
